--- a/Roster_Builder/Staff Database.xlsx
+++ b/Roster_Builder/Staff Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dimeji/Downloads/Conductor/Salary List/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAB278B3-8611-8646-BA6F-58256FB5C0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BBCB24-212F-CE47-B564-15CF8CE2B867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7700" yWindow="500" windowWidth="28840" windowHeight="20500" activeTab="1" xr2:uid="{6267D948-9A52-A142-9D60-59C70181BE48}"/>
+    <workbookView xWindow="7700" yWindow="500" windowWidth="28840" windowHeight="20500" xr2:uid="{6267D948-9A52-A142-9D60-59C70181BE48}"/>
   </bookViews>
   <sheets>
     <sheet name="RadioNo" sheetId="1" r:id="rId1"/>
@@ -547,12 +547,15 @@
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.83203125" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
@@ -837,12 +840,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8FDC5C-CE6A-8449-8752-8948C915EEF3}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.83203125" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C1" t="s">
@@ -864,7 +870,7 @@
       <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>58</v>
       </c>
       <c r="C3" t="s">
